--- a/final_data_pipeline/output/312120longform.xlsx
+++ b/final_data_pipeline/output/312120longform.xlsx
@@ -1709,7 +1709,7 @@
         <v>76</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AB12">
         <v>8000</v>
@@ -1798,7 +1798,7 @@
         <v>76</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AB13">
         <v>8000</v>
@@ -1890,7 +1890,7 @@
         <v>76</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AB14">
         <v>8000</v>
@@ -1982,7 +1982,7 @@
         <v>76</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AB15">
         <v>8000</v>
@@ -2077,7 +2077,7 @@
         <v>76</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AB16">
         <v>8000</v>
@@ -2166,7 +2166,7 @@
         <v>76</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AB17">
         <v>8000</v>
@@ -2255,7 +2255,7 @@
         <v>76</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AB18">
         <v>8000</v>
@@ -2344,7 +2344,7 @@
         <v>76</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AB19">
         <v>8000</v>
@@ -2433,7 +2433,7 @@
         <v>76</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AB20">
         <v>8000</v>
@@ -2522,7 +2522,7 @@
         <v>76</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AB21">
         <v>8000</v>
@@ -2614,7 +2614,7 @@
         <v>76</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB22">
         <v>8000</v>
@@ -2709,7 +2709,7 @@
         <v>76</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB23">
         <v>8000</v>
@@ -2798,7 +2798,7 @@
         <v>76</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB24">
         <v>8000</v>
@@ -2887,7 +2887,7 @@
         <v>76</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB25">
         <v>8000</v>
@@ -2976,7 +2976,7 @@
         <v>76</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB26">
         <v>8000</v>
@@ -8943,7 +8943,7 @@
         <v>76</v>
       </c>
       <c r="AA92">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB92">
         <v>8000</v>
@@ -9032,7 +9032,7 @@
         <v>76</v>
       </c>
       <c r="AA93">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB93">
         <v>8000</v>
@@ -9121,7 +9121,7 @@
         <v>76</v>
       </c>
       <c r="AA94">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB94">
         <v>8000</v>
@@ -9210,7 +9210,7 @@
         <v>76</v>
       </c>
       <c r="AA95">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB95">
         <v>8000</v>
@@ -9302,7 +9302,7 @@
         <v>76</v>
       </c>
       <c r="AA96">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB96">
         <v>8000</v>
@@ -9397,7 +9397,7 @@
         <v>76</v>
       </c>
       <c r="AA97">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB97">
         <v>8000</v>
@@ -9486,7 +9486,7 @@
         <v>76</v>
       </c>
       <c r="AA98">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB98">
         <v>8000</v>
@@ -9575,7 +9575,7 @@
         <v>76</v>
       </c>
       <c r="AA99">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB99">
         <v>8000</v>
@@ -9667,7 +9667,7 @@
         <v>76</v>
       </c>
       <c r="AA100">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB100">
         <v>8000</v>
@@ -9762,7 +9762,7 @@
         <v>76</v>
       </c>
       <c r="AA101">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB101">
         <v>8000</v>
@@ -10753,7 +10753,7 @@
         <v>76</v>
       </c>
       <c r="AA112">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB112">
         <v>8000</v>
@@ -10842,7 +10842,7 @@
         <v>76</v>
       </c>
       <c r="AA113">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB113">
         <v>8000</v>
@@ -10931,7 +10931,7 @@
         <v>76</v>
       </c>
       <c r="AA114">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB114">
         <v>8000</v>
@@ -11020,7 +11020,7 @@
         <v>76</v>
       </c>
       <c r="AA115">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB115">
         <v>8000</v>
@@ -11112,7 +11112,7 @@
         <v>76</v>
       </c>
       <c r="AA116">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB116">
         <v>8000</v>
@@ -11207,7 +11207,7 @@
         <v>76</v>
       </c>
       <c r="AA117">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB117">
         <v>8000</v>
@@ -11296,7 +11296,7 @@
         <v>76</v>
       </c>
       <c r="AA118">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB118">
         <v>8000</v>
@@ -11385,7 +11385,7 @@
         <v>76</v>
       </c>
       <c r="AA119">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB119">
         <v>8000</v>
@@ -11477,7 +11477,7 @@
         <v>76</v>
       </c>
       <c r="AA120">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB120">
         <v>8000</v>
@@ -11575,7 +11575,7 @@
         <v>76</v>
       </c>
       <c r="AA121">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB121">
         <v>8000</v>
@@ -11670,7 +11670,7 @@
         <v>76</v>
       </c>
       <c r="AA122">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB122">
         <v>8000</v>
@@ -11759,7 +11759,7 @@
         <v>76</v>
       </c>
       <c r="AA123">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB123">
         <v>8000</v>
@@ -11848,7 +11848,7 @@
         <v>76</v>
       </c>
       <c r="AA124">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB124">
         <v>8000</v>
@@ -11937,7 +11937,7 @@
         <v>76</v>
       </c>
       <c r="AA125">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB125">
         <v>8000</v>
@@ -12026,7 +12026,7 @@
         <v>76</v>
       </c>
       <c r="AA126">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB126">
         <v>8000</v>
@@ -14373,7 +14373,7 @@
         <v>76</v>
       </c>
       <c r="AA152">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB152">
         <v>8000</v>
@@ -14462,7 +14462,7 @@
         <v>76</v>
       </c>
       <c r="AA153">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB153">
         <v>8000</v>
@@ -14551,7 +14551,7 @@
         <v>76</v>
       </c>
       <c r="AA154">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB154">
         <v>8000</v>
@@ -14640,7 +14640,7 @@
         <v>76</v>
       </c>
       <c r="AA155">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB155">
         <v>8000</v>
@@ -14732,7 +14732,7 @@
         <v>76</v>
       </c>
       <c r="AA156">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB156">
         <v>8000</v>
@@ -14821,7 +14821,7 @@
         <v>76</v>
       </c>
       <c r="AA157">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB157">
         <v>8000</v>
@@ -14910,7 +14910,7 @@
         <v>76</v>
       </c>
       <c r="AA158">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB158">
         <v>8000</v>
@@ -14999,7 +14999,7 @@
         <v>76</v>
       </c>
       <c r="AA159">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB159">
         <v>8000</v>
@@ -15088,7 +15088,7 @@
         <v>76</v>
       </c>
       <c r="AA160">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB160">
         <v>8000</v>
@@ -15180,7 +15180,7 @@
         <v>76</v>
       </c>
       <c r="AA161">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB161">
         <v>8000</v>
